--- a/experiment_tracker.xlsx
+++ b/experiment_tracker.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20379"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20385"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Geisler Lab\camouflage-detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1EF73A0-84A4-415B-942A-7BAF59149A69}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC94726-5F5D-4643-B703-9B8AE6DA5082}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>pink noise</t>
   </si>
@@ -33,18 +33,12 @@
     <t>pink noise, unblocked</t>
   </si>
   <si>
-    <t>noise colour</t>
-  </si>
-  <si>
     <t>moth</t>
   </si>
   <si>
     <t>rock</t>
   </si>
   <si>
-    <t>spots</t>
-  </si>
-  <si>
     <t>bark</t>
   </si>
   <si>
@@ -63,9 +57,6 @@
     <t>pink noise, ecc</t>
   </si>
   <si>
-    <t>noise colour, ecc</t>
-  </si>
-  <si>
     <t>whitened</t>
   </si>
   <si>
@@ -75,9 +66,6 @@
     <t>luminance</t>
   </si>
   <si>
-    <t>Me</t>
-  </si>
-  <si>
     <t>Anqi</t>
   </si>
   <si>
@@ -87,10 +75,25 @@
     <t>Only 2 subjects:</t>
   </si>
   <si>
-    <t>flipped?</t>
-  </si>
-  <si>
     <t>soil</t>
+  </si>
+  <si>
+    <t>grass (Brodatz)</t>
+  </si>
+  <si>
+    <t>paper (Brodatz)</t>
+  </si>
+  <si>
+    <t>spots (Brodatz inverted)</t>
+  </si>
+  <si>
+    <t>Neel</t>
+  </si>
+  <si>
+    <t>texture exponent</t>
+  </si>
+  <si>
+    <t>texture exponent, ecc</t>
   </si>
 </sst>
 </file>
@@ -114,13 +117,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C5700"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -134,11 +137,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -146,37 +155,21 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
-    <cellStyle name="Input" xfId="2" builtinId="20"/>
+    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -489,35 +482,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -525,111 +515,209 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D4" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>3</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="4"/>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>4</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>9</v>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="B12" s="1"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B13" s="1"/>
-      <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
-      <c r="E14" s="3"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="1"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19" s="1"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>3</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>4</v>
+      </c>
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>6</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>8</v>
+      </c>
+      <c r="B23" s="1"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>9</v>
+      </c>
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>10</v>
+      </c>
+      <c r="B25" s="1"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>12</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>3</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>6</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>9</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>12</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="1"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="1"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B37" s="1"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="1"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="1"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="1"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="1"/>
+      <c r="B38" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/experiment_tracker.xlsx
+++ b/experiment_tracker.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20385"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Geisler Lab\camouflage-detection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Abhranil\OneDrive - The University of Texas at Austin\Geisler Lab\camouflage_detection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC94726-5F5D-4643-B703-9B8AE6DA5082}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15345"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,14 +24,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>pink noise</t>
   </si>
   <si>
-    <t>pink noise, unblocked</t>
-  </si>
-  <si>
     <t>moth</t>
   </si>
   <si>
@@ -60,12 +56,6 @@
     <t>whitened</t>
   </si>
   <si>
-    <t>duration, contrast, target size</t>
-  </si>
-  <si>
-    <t>luminance</t>
-  </si>
-  <si>
     <t>Anqi</t>
   </si>
   <si>
@@ -94,13 +84,46 @@
   </si>
   <si>
     <t>texture exponent, ecc</t>
+  </si>
+  <si>
+    <t>shape exponent, at diff tx exponents</t>
+  </si>
+  <si>
+    <t>4/16</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>hardest 6 levels only</t>
+  </si>
+  <si>
+    <t>distance</t>
+  </si>
+  <si>
+    <t>contrast, luminance</t>
+  </si>
+  <si>
+    <t>Sid</t>
+  </si>
+  <si>
+    <t>diff target and background textures</t>
+  </si>
+  <si>
+    <t>pink noise, shuffled</t>
+  </si>
+  <si>
+    <t>Behnam</t>
+  </si>
+  <si>
+    <t>camo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,8 +145,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -146,6 +183,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -156,18 +199,24 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="20% - Accent6" xfId="3" builtinId="50"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -481,246 +530,642 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D38"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="1">
+        <v>2430</v>
+      </c>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="1"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>3</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>4</v>
+      </c>
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>6</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>8</v>
+      </c>
+      <c r="B24" s="1"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>9</v>
+      </c>
+      <c r="C25" s="1"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>10</v>
+      </c>
+      <c r="B26" s="1"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>12</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="1"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>2</v>
-      </c>
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
-        <v>3</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>4</v>
-      </c>
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>6</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>8</v>
-      </c>
-      <c r="B23" s="1"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>9</v>
-      </c>
-      <c r="C24" s="1"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>10</v>
-      </c>
-      <c r="B25" s="1"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>12</v>
-      </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>3</v>
-      </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>10</v>
-      </c>
-      <c r="B34" s="1"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>11</v>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>12</v>
+      </c>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>0.8</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>0.9</v>
       </c>
       <c r="B37" s="1"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="C37" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>1</v>
+      </c>
+      <c r="B38" s="1"/>
+      <c r="C38" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B39" s="1"/>
+      <c r="C39" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>1.2</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>1</v>
+      </c>
+      <c r="B43" s="1"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>0.5</v>
+      </c>
+      <c r="B44" s="1"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>12</v>
       </c>
-      <c r="B38" s="1"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>50</v>
+      </c>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>100</v>
+      </c>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>400</v>
+      </c>
+      <c r="B52" s="1"/>
+      <c r="C52" s="5"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>800</v>
+      </c>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>80</v>
+      </c>
+      <c r="B56" s="1"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>100</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>120</v>
+      </c>
+      <c r="B58" s="1"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>140</v>
+      </c>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>160</v>
+      </c>
+      <c r="B60" s="1"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100855712E6B7FD8D4A913381E899A0EFA8" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6e2b09040751d1ce7e4b02845c153c59">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="304499b8-13b5-4b05-a5d6-8b0e4653f51e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8417416d521ce5b7110641efce3be348" ns3:_="">
+    <xsd:import namespace="304499b8-13b5-4b05-a5d6-8b0e4653f51e"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="304499b8-13b5-4b05-a5d6-8b0e4653f51e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="11" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="12" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="14" nillable="true" ma:displayName="MediaServiceDateTaken" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="15" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6495D215-A247-42AC-AD29-58DFCEC1EC21}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="304499b8-13b5-4b05-a5d6-8b0e4653f51e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA309006-4ABC-4D49-BFE5-F4F90E95876E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="304499b8-13b5-4b05-a5d6-8b0e4653f51e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59401AFC-0DEB-4E38-9E61-29371722D826}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/experiment_tracker.xlsx
+++ b/experiment_tracker.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Abhranil\OneDrive - The University of Texas at Austin\Geisler Lab\camouflage_detection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utexas-my.sharepoint.com/personal/adas_chaos_utexas_edu/Documents/Geisler Lab/camouflage_detection/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_106DC86DC7B27A6CA9CE96565E78D5FBAE0A82C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10F91AD4-E3D2-43CA-B6E2-FA277E10F364}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15345"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>pink noise</t>
   </si>
@@ -74,9 +75,6 @@
     <t>paper (Brodatz)</t>
   </si>
   <si>
-    <t>spots (Brodatz inverted)</t>
-  </si>
-  <si>
     <t>Neel</t>
   </si>
   <si>
@@ -117,12 +115,21 @@
   </si>
   <si>
     <t>camo</t>
+  </si>
+  <si>
+    <t>camo large</t>
+  </si>
+  <si>
+    <t>spots</t>
+  </si>
+  <si>
+    <t>amount paid:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -530,8 +537,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F63"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.42578125" bestFit="1" customWidth="1"/>
@@ -540,7 +547,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C1" t="s">
         <v>10</v>
@@ -549,37 +556,35 @@
         <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1">
-        <v>2430</v>
-      </c>
-      <c r="F2" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="F2">
+        <v>200</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="E3" s="1">
+        <v>2430</v>
+      </c>
       <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -587,27 +592,29 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -616,34 +623,33 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
+      <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>13</v>
+      <c r="A12" t="s">
+        <v>7</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -652,16 +658,18 @@
       <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>14</v>
+      <c r="A13" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -671,264 +679,281 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="B18" s="1"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B17" s="1"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B19" s="1"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>2</v>
       </c>
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
         <v>3</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="C23" s="1"/>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24">
         <v>4</v>
       </c>
-      <c r="B22" s="1"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="B24" s="1"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
         <v>6</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>8</v>
       </c>
-      <c r="B24" s="1"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="B26" s="1"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
         <v>9</v>
       </c>
-      <c r="C25" s="1"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26">
+      <c r="C27" s="1"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28">
         <v>10</v>
       </c>
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="B28" s="1"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
         <v>12</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30">
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32">
         <v>3</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>6</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>9</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
     </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>9</v>
+      </c>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+    </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>0.8</v>
-      </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
+      <c r="A35">
+        <v>12</v>
+      </c>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>0.9</v>
-      </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="4" t="s">
-        <v>21</v>
+      <c r="A37" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="B38" s="1"/>
-      <c r="C38" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="C38" s="1"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>1.1000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
+        <v>1</v>
+      </c>
+      <c r="B40" s="1"/>
+      <c r="C40" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B41" s="1"/>
+      <c r="C41" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
         <v>1.2</v>
       </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43">
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
         <v>1</v>
       </c>
-      <c r="B43" s="1"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44">
+      <c r="B45" s="1"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
         <v>0.5</v>
       </c>
-      <c r="B44" s="1"/>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>9</v>
-      </c>
       <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>50</v>
-      </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-    </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>100</v>
-      </c>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
+      <c r="A51" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="B52" s="1"/>
-      <c r="C52" s="5"/>
+      <c r="C52" s="1"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
+        <v>100</v>
+      </c>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>400</v>
+      </c>
+      <c r="B54" s="1"/>
+      <c r="C54" s="5"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
         <v>800</v>
       </c>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1" t="s">
+      <c r="B55" s="1"/>
+      <c r="C55" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" s="2">
-        <v>80</v>
-      </c>
-      <c r="B56" s="1"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>100</v>
-      </c>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="B58" s="1"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60">
+      <c r="A60" s="2">
+        <v>120</v>
+      </c>
+      <c r="B60" s="1"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>140</v>
+      </c>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
         <v>160</v>
       </c>
-      <c r="B60" s="1"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>25</v>
+      <c r="B62" s="1"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1114,18 +1139,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1147,6 +1172,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59401AFC-0DEB-4E38-9E61-29371722D826}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA309006-4ABC-4D49-BFE5-F4F90E95876E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
@@ -1160,12 +1193,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59401AFC-0DEB-4E38-9E61-29371722D826}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>